--- a/sample-data/CRM储备项目运营复盘助手-脱敏模拟数据.xlsx
+++ b/sample-data/CRM储备项目运营复盘助手-脱敏模拟数据.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目明细（标准导入）" sheetId="1" r:id="R5df410aa36024650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试预期结果" sheetId="2" r:id="Rbc1c6c2d3c844001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="3" r:id="R38f4db020dfd427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目明细（标准导入）" sheetId="1" r:id="Rc0f7ad0e776b48cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试预期结果" sheetId="2" r:id="Rf9de9242aca2408e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="3" r:id="R2cdc0e1abf4c41f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -465,13 +465,13 @@
         <x:v>P-2026-001</x:v>
       </x:c>
       <x:c r="B4" s="18" t="str">
-        <x:v>南昌轨道维保项目</x:v>
+        <x:v>星港轨道维保项目</x:v>
       </x:c>
       <x:c r="C4" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -498,7 +498,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M4" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N4" s="18" t="str">
         <x:v>维保项目</x:v>
@@ -512,13 +512,13 @@
         <x:v>P-2026-002</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>赣州水利监测项目</x:v>
+        <x:v>云川水利监测项目</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E5" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -545,7 +545,7 @@
         <x:v>水利</x:v>
       </x:c>
       <x:c r="M5" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N5" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -559,13 +559,13 @@
         <x:v>P-2026-003</x:v>
       </x:c>
       <x:c r="B6" s="18" t="str">
-        <x:v>九江桥梁检测项目</x:v>
+        <x:v>北原桥梁检测项目</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -592,7 +592,7 @@
         <x:v>桥梁</x:v>
       </x:c>
       <x:c r="M6" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N6" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -606,13 +606,13 @@
         <x:v>P-2026-004</x:v>
       </x:c>
       <x:c r="B7" s="18" t="str">
-        <x:v>宜春地灾预警项目</x:v>
+        <x:v>青原地灾预警项目</x:v>
       </x:c>
       <x:c r="C7" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
         <x:v>已签约</x:v>
@@ -639,7 +639,7 @@
         <x:v>地质灾害</x:v>
       </x:c>
       <x:c r="M7" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N7" s="18" t="str">
         <x:v>人工项目</x:v>
@@ -653,13 +653,13 @@
         <x:v>P-2026-005</x:v>
       </x:c>
       <x:c r="B8" s="18" t="str">
-        <x:v>武汉市政运维项目</x:v>
+        <x:v>海岬市政运维项目</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -686,7 +686,7 @@
         <x:v>市政</x:v>
       </x:c>
       <x:c r="M8" s="18" t="str">
-        <x:v>湖北省</x:v>
+        <x:v>示例区域乙</x:v>
       </x:c>
       <x:c r="N8" s="18" t="str">
         <x:v>维保项目</x:v>
@@ -700,13 +700,13 @@
         <x:v>P-2026-006</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
-        <x:v>长沙软件平台项目</x:v>
+        <x:v>远景软件平台项目</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -733,7 +733,7 @@
         <x:v>软件</x:v>
       </x:c>
       <x:c r="M9" s="18" t="str">
-        <x:v>湖南省</x:v>
+        <x:v>示例区域丙</x:v>
       </x:c>
       <x:c r="N9" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -747,13 +747,13 @@
         <x:v>P-2026-007</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
-        <x:v>重庆隧道巡检项目</x:v>
+        <x:v>江畔隧道巡检项目</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -780,7 +780,7 @@
         <x:v>隧道</x:v>
       </x:c>
       <x:c r="M10" s="18" t="str">
-        <x:v>重庆市</x:v>
+        <x:v>示例区域丁</x:v>
       </x:c>
       <x:c r="N10" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -794,13 +794,13 @@
         <x:v>P-2026-008</x:v>
       </x:c>
       <x:c r="B11" s="18" t="str">
-        <x:v>成都交通设施项目</x:v>
+        <x:v>星港交通设施项目</x:v>
       </x:c>
       <x:c r="C11" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
         <x:v>丢单</x:v>
@@ -827,7 +827,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M11" s="18" t="str">
-        <x:v>四川省</x:v>
+        <x:v>示例区域戊</x:v>
       </x:c>
       <x:c r="N11" s="18" t="str">
         <x:v>产品</x:v>
@@ -841,13 +841,13 @@
         <x:v>P-2026-009</x:v>
       </x:c>
       <x:c r="B12" s="18" t="str">
-        <x:v>合肥建筑物监测项目</x:v>
+        <x:v>云川建筑物监测项目</x:v>
       </x:c>
       <x:c r="C12" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D12" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -874,7 +874,7 @@
         <x:v>建筑物</x:v>
       </x:c>
       <x:c r="M12" s="18" t="str">
-        <x:v>安徽省</x:v>
+        <x:v>示例区域己</x:v>
       </x:c>
       <x:c r="N12" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -888,13 +888,13 @@
         <x:v>P-2026-010</x:v>
       </x:c>
       <x:c r="B13" s="18" t="str">
-        <x:v>南京基坑监测项目</x:v>
+        <x:v>北原基坑监测项目</x:v>
       </x:c>
       <x:c r="C13" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -921,7 +921,7 @@
         <x:v>基坑</x:v>
       </x:c>
       <x:c r="M13" s="18" t="str">
-        <x:v>江苏省</x:v>
+        <x:v>示例区域庚</x:v>
       </x:c>
       <x:c r="N13" s="18" t="str">
         <x:v>人工项目</x:v>
@@ -935,13 +935,13 @@
         <x:v>P-2026-011</x:v>
       </x:c>
       <x:c r="B14" s="18" t="str">
-        <x:v>上海智能交通项目</x:v>
+        <x:v>海岬智能交通项目</x:v>
       </x:c>
       <x:c r="C14" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -968,7 +968,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M14" s="18" t="str">
-        <x:v>上海市</x:v>
+        <x:v>示例区域辛</x:v>
       </x:c>
       <x:c r="N14" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -982,13 +982,13 @@
         <x:v>P-2026-012</x:v>
       </x:c>
       <x:c r="B15" s="18" t="str">
-        <x:v>杭州桥梁养护项目</x:v>
+        <x:v>青原桥梁养护项目</x:v>
       </x:c>
       <x:c r="C15" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
         <x:v>已签约</x:v>
@@ -1015,7 +1015,7 @@
         <x:v>桥梁</x:v>
       </x:c>
       <x:c r="M15" s="18" t="str">
-        <x:v>浙江省</x:v>
+        <x:v>示例区域壬</x:v>
       </x:c>
       <x:c r="N15" s="18" t="str">
         <x:v>维保项目</x:v>
@@ -1029,13 +1029,13 @@
         <x:v>P-2026-013</x:v>
       </x:c>
       <x:c r="B16" s="18" t="str">
-        <x:v>南昌水利巡检项目</x:v>
+        <x:v>远景水利巡检项目</x:v>
       </x:c>
       <x:c r="C16" s="18" t="str">
         <x:v>营销四部</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
-        <x:v>赵敏</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="E16" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1062,7 +1062,7 @@
         <x:v>水利</x:v>
       </x:c>
       <x:c r="M16" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N16" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -1076,13 +1076,13 @@
         <x:v>P-2026-014</x:v>
       </x:c>
       <x:c r="B17" s="18" t="str">
-        <x:v>景德镇地灾治理项目</x:v>
+        <x:v>星港地灾治理项目</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
         <x:v>营销四部</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>赵敏</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>地质灾害</x:v>
       </x:c>
       <x:c r="M17" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N17" s="18" t="str">
         <x:v>人工项目</x:v>
@@ -1123,13 +1123,13 @@
         <x:v>P-2026-015</x:v>
       </x:c>
       <x:c r="B18" s="18" t="str">
-        <x:v>厦门港口安全项目</x:v>
+        <x:v>云川港口安全项目</x:v>
       </x:c>
       <x:c r="C18" s="18" t="str">
         <x:v>营销四部</x:v>
       </x:c>
       <x:c r="D18" s="18" t="str">
-        <x:v>赵敏</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1156,7 +1156,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M18" s="18" t="str">
-        <x:v>福建省</x:v>
+        <x:v>示例区域癸</x:v>
       </x:c>
       <x:c r="N18" s="18" t="str">
         <x:v>产品</x:v>
@@ -1170,13 +1170,13 @@
         <x:v>P-2026-016</x:v>
       </x:c>
       <x:c r="B19" s="18" t="str">
-        <x:v>广州园区物联项目</x:v>
+        <x:v>北原园区物联项目</x:v>
       </x:c>
       <x:c r="C19" s="18" t="str">
         <x:v>营销四部</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
-        <x:v>赵敏</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1203,7 +1203,7 @@
         <x:v>软件</x:v>
       </x:c>
       <x:c r="M19" s="18" t="str">
-        <x:v>广东省</x:v>
+        <x:v>示例区域子</x:v>
       </x:c>
       <x:c r="N19" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -1217,13 +1217,13 @@
         <x:v>P-2026-017</x:v>
       </x:c>
       <x:c r="B20" s="18" t="str">
-        <x:v>南昌道路检测项目</x:v>
+        <x:v>星港道路检测项目</x:v>
       </x:c>
       <x:c r="C20" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1250,7 +1250,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M20" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N20" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -1264,13 +1264,13 @@
         <x:v>P-2026-018</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>宜昌水库监测项目</x:v>
+        <x:v>云川水库监测项目</x:v>
       </x:c>
       <x:c r="C21" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1297,7 +1297,7 @@
         <x:v>水利</x:v>
       </x:c>
       <x:c r="M21" s="18" t="str">
-        <x:v>湖北省</x:v>
+        <x:v>示例区域乙</x:v>
       </x:c>
       <x:c r="N21" s="18" t="str">
         <x:v>维保项目</x:v>
@@ -1311,13 +1311,13 @@
         <x:v>P-2026-019</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>南京隧道运维项目</x:v>
+        <x:v>北原隧道运维项目</x:v>
       </x:c>
       <x:c r="C22" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D22" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>隧道</x:v>
       </x:c>
       <x:c r="M22" s="18" t="str">
-        <x:v>江苏省</x:v>
+        <x:v>示例区域庚</x:v>
       </x:c>
       <x:c r="N22" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -1358,13 +1358,13 @@
         <x:v>P-2026-020</x:v>
       </x:c>
       <x:c r="B23" s="18" t="str">
-        <x:v>深圳软件升级项目</x:v>
+        <x:v>海岬软件升级项目</x:v>
       </x:c>
       <x:c r="C23" s="18" t="str">
         <x:v>营销四部</x:v>
       </x:c>
       <x:c r="D23" s="18" t="str">
-        <x:v>赵敏</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1391,7 +1391,7 @@
         <x:v>软件</x:v>
       </x:c>
       <x:c r="M23" s="18" t="str">
-        <x:v>广东省</x:v>
+        <x:v>示例区域子</x:v>
       </x:c>
       <x:c r="N23" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -1405,13 +1405,13 @@
         <x:v>P-2026-021</x:v>
       </x:c>
       <x:c r="B24" s="18" t="str">
-        <x:v>武汉桥梁加固项目</x:v>
+        <x:v>江畔桥梁加固项目</x:v>
       </x:c>
       <x:c r="C24" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D24" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1438,7 +1438,7 @@
         <x:v>桥梁</x:v>
       </x:c>
       <x:c r="M24" s="18" t="str">
-        <x:v>湖北省</x:v>
+        <x:v>示例区域乙</x:v>
       </x:c>
       <x:c r="N24" s="18" t="str">
         <x:v>人工项目</x:v>
@@ -1452,13 +1452,13 @@
         <x:v>P-2026-022</x:v>
       </x:c>
       <x:c r="B25" s="18" t="str">
-        <x:v>南昌智慧停车项目</x:v>
+        <x:v>星港智慧停车项目</x:v>
       </x:c>
       <x:c r="C25" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D25" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1485,7 +1485,7 @@
         <x:v>市政</x:v>
       </x:c>
       <x:c r="M25" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N25" s="18" t="str">
         <x:v>产品</x:v>
@@ -1499,13 +1499,13 @@
         <x:v>P-2026-023</x:v>
       </x:c>
       <x:c r="B26" s="18" t="str">
-        <x:v>华中交通数字化项目</x:v>
+        <x:v>远景交通数字化项目</x:v>
       </x:c>
       <x:c r="C26" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D26" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E26" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1532,7 +1532,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M26" s="18" t="str">
-        <x:v>湖北省</x:v>
+        <x:v>示例区域乙</x:v>
       </x:c>
       <x:c r="N26" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -1546,13 +1546,13 @@
         <x:v>P-2026-024</x:v>
       </x:c>
       <x:c r="B27" s="18" t="str">
-        <x:v>西南综合管廊项目</x:v>
+        <x:v>远景综合管廊项目</x:v>
       </x:c>
       <x:c r="C27" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D27" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E27" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1579,7 +1579,7 @@
         <x:v>市政</x:v>
       </x:c>
       <x:c r="M27" s="18" t="str">
-        <x:v>重庆市</x:v>
+        <x:v>示例区域丁</x:v>
       </x:c>
       <x:c r="N27" s="18" t="str">
         <x:v>人工项目</x:v>
@@ -1593,13 +1593,13 @@
         <x:v>P-2026-025</x:v>
       </x:c>
       <x:c r="B28" s="18" t="str">
-        <x:v>赣州河道治理项目</x:v>
+        <x:v>云川河道治理项目</x:v>
       </x:c>
       <x:c r="C28" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D28" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E28" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1624,7 +1624,7 @@
         <x:v>水利</x:v>
       </x:c>
       <x:c r="M28" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N28" s="18" t="str">
         <x:v>维保项目</x:v>
@@ -1638,13 +1638,13 @@
         <x:v>P-2026-026</x:v>
       </x:c>
       <x:c r="B29" s="18" t="str">
-        <x:v>南昌轨道维保项目</x:v>
+        <x:v>星港轨道维保项目</x:v>
       </x:c>
       <x:c r="C29" s="18" t="str">
         <x:v>营销一部</x:v>
       </x:c>
       <x:c r="D29" s="18" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>示例经理甲</x:v>
       </x:c>
       <x:c r="E29" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M29" s="18" t="str">
-        <x:v>江西省</x:v>
+        <x:v>示例区域甲</x:v>
       </x:c>
       <x:c r="N29" s="18" t="str">
         <x:v>维保项目</x:v>
@@ -1685,13 +1685,13 @@
         <x:v>P-2026-027</x:v>
       </x:c>
       <x:c r="B30" s="18" t="str">
-        <x:v>宁波港区安防项目</x:v>
+        <x:v>海岬港区安防项目</x:v>
       </x:c>
       <x:c r="C30" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D30" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E30" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1718,7 +1718,7 @@
         <x:v>交通</x:v>
       </x:c>
       <x:c r="M30" s="18" t="str">
-        <x:v>浙江省</x:v>
+        <x:v>示例区域壬</x:v>
       </x:c>
       <x:c r="N30" s="18" t="str">
         <x:v>产品</x:v>
@@ -1732,13 +1732,13 @@
         <x:v>P-2026-028</x:v>
       </x:c>
       <x:c r="B31" s="18" t="str">
-        <x:v>长沙城市内涝项目</x:v>
+        <x:v>远景城市内涝项目</x:v>
       </x:c>
       <x:c r="C31" s="18" t="str">
         <x:v>营销二部</x:v>
       </x:c>
       <x:c r="D31" s="18" t="str">
-        <x:v>李航</x:v>
+        <x:v>示例经理乙</x:v>
       </x:c>
       <x:c r="E31" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1765,7 +1765,7 @@
         <x:v>市政</x:v>
       </x:c>
       <x:c r="M31" s="18" t="str">
-        <x:v>湖南省</x:v>
+        <x:v>示例区域丙</x:v>
       </x:c>
       <x:c r="N31" s="18" t="str">
         <x:v>在线项目</x:v>
@@ -1779,13 +1779,13 @@
         <x:v>P-2026-029</x:v>
       </x:c>
       <x:c r="B32" s="18" t="str">
-        <x:v>合肥城市更新项目</x:v>
+        <x:v>青原城市更新项目</x:v>
       </x:c>
       <x:c r="C32" s="18" t="str">
         <x:v>营销三部</x:v>
       </x:c>
       <x:c r="D32" s="18" t="str">
-        <x:v>王宁</x:v>
+        <x:v>示例经理丙</x:v>
       </x:c>
       <x:c r="E32" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1812,7 +1812,7 @@
         <x:v>建筑物</x:v>
       </x:c>
       <x:c r="M32" s="18" t="str">
-        <x:v>安徽省</x:v>
+        <x:v>示例区域己</x:v>
       </x:c>
       <x:c r="N32" s="18" t="str">
         <x:v>人工项目</x:v>
@@ -1826,13 +1826,13 @@
         <x:v>P-2026-030</x:v>
       </x:c>
       <x:c r="B33" s="18" t="str">
-        <x:v>福州软件运维项目</x:v>
+        <x:v>星港软件运维项目</x:v>
       </x:c>
       <x:c r="C33" s="18" t="str">
         <x:v>营销四部</x:v>
       </x:c>
       <x:c r="D33" s="18" t="str">
-        <x:v>赵敏</x:v>
+        <x:v>示例经理丁</x:v>
       </x:c>
       <x:c r="E33" s="18" t="str">
         <x:v>跟进中</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>软件</x:v>
       </x:c>
       <x:c r="M33" s="18" t="str">
-        <x:v>福建省</x:v>
+        <x:v>示例区域癸</x:v>
       </x:c>
       <x:c r="N33" s="18" t="str">
         <x:v>软件项目</x:v>
@@ -1886,7 +1886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7629f5af7754407e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac1b65a265494caf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1906,6 +1906,11 @@
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="str">
@@ -2054,6 +2059,12 @@
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="str">
         <x:v>字段</x:v>
